--- a/backend/archives/2026-05/GHI-May-2026.xlsx
+++ b/backend/archives/2026-05/GHI-May-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
   <si>
     <t>Field</t>
   </si>
@@ -96,6 +96,12 @@
   </si>
   <si>
     <t>5/5/2026</t>
+  </si>
+  <si>
+    <t>GHI260500002</t>
+  </si>
+  <si>
+    <t>23/5/2026</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -559,7 +565,7 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -567,7 +573,7 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>7539</v>
+        <v>12079</v>
       </c>
     </row>
   </sheetData>
@@ -578,7 +584,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -677,33 +683,62 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="3">
-        <v>7539</v>
-      </c>
-      <c r="D4" s="3">
-        <v>6157</v>
-      </c>
-      <c r="E4" s="3">
-        <v>4679</v>
-      </c>
-      <c r="F4" s="3">
+      <c r="C4">
+        <v>4540</v>
+      </c>
+      <c r="D4">
+        <v>8066</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>3525</v>
+      </c>
+      <c r="I4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="3">
+        <v>12079</v>
+      </c>
+      <c r="D5" s="3">
+        <v>14223</v>
+      </c>
+      <c r="E5" s="3">
+        <v>4681</v>
+      </c>
+      <c r="F5" s="3">
         <v>5</v>
       </c>
-      <c r="G4" s="3">
-        <v>2</v>
-      </c>
-      <c r="H4" s="3">
-        <v>-6064</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>29</v>
+      <c r="G5" s="3">
+        <v>4</v>
+      </c>
+      <c r="H5" s="3">
+        <v>-2539</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
